--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -687,6 +687,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>1526: fixed value = http://loinc.org#9825-1 Mycobacterium sp identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1828,7 +1831,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="151.1796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -3970,36 +3973,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4022,19 +4025,19 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>84</v>
@@ -4083,7 +4086,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4104,19 +4107,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4124,10 +4127,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4150,16 +4153,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4209,7 +4212,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4236,13 +4239,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4250,14 +4253,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4276,19 +4279,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4337,7 +4340,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4358,19 +4361,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4378,14 +4381,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4404,19 +4407,19 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -4465,7 +4468,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4474,10 +4477,10 @@
         <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4486,19 +4489,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4506,10 +4509,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4532,16 +4535,16 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4591,7 +4594,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>82</v>
@@ -4618,13 +4621,13 @@
         <v>84</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4632,10 +4635,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4658,17 +4661,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4717,7 +4720,7 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4738,19 +4741,19 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4758,10 +4761,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4784,19 +4787,19 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4833,7 +4836,7 @@
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
@@ -4843,7 +4846,7 @@
         <v>199</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -4852,10 +4855,10 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -4867,30 +4870,30 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>84</v>
@@ -4912,19 +4915,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -4973,7 +4976,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>82</v>
@@ -4982,13 +4985,13 @@
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
@@ -4997,27 +5000,27 @@
         <v>84</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5043,16 +5046,16 @@
         <v>191</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5081,7 +5084,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>84</v>
@@ -5099,7 +5102,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5108,7 +5111,7 @@
         <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>106</v>
@@ -5129,7 +5132,7 @@
         <v>137</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5140,14 +5143,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5169,16 +5172,16 @@
         <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5206,10 +5209,10 @@
         <v>211</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>84</v>
@@ -5227,7 +5230,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5251,27 +5254,27 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5294,19 +5297,19 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5355,7 +5358,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5382,10 +5385,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5396,10 +5399,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5425,13 +5428,13 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5457,13 +5460,13 @@
         <v>84</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>84</v>
@@ -5481,7 +5484,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5505,27 +5508,27 @@
         <v>84</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5551,16 +5554,16 @@
         <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5585,13 +5588,13 @@
         <v>84</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>84</v>
@@ -5609,7 +5612,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5636,10 +5639,10 @@
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -5650,10 +5653,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5676,16 +5679,16 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5735,7 +5738,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5759,27 +5762,27 @@
         <v>84</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5802,16 +5805,16 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5861,7 +5864,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5885,27 +5888,27 @@
         <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5928,19 +5931,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -5989,7 +5992,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6001,7 +6004,7 @@
         <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6016,10 +6019,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6030,10 +6033,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6056,13 +6059,13 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6113,7 +6116,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6143,7 +6146,7 @@
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6154,10 +6157,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6186,7 +6189,7 @@
         <v>141</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>143</v>
@@ -6239,7 +6242,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6269,7 +6272,7 @@
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6280,14 +6283,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6309,10 +6312,10 @@
         <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>143</v>
@@ -6367,7 +6370,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6408,10 +6411,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6434,13 +6437,13 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6491,7 +6494,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6500,7 +6503,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6518,10 +6521,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6532,10 +6535,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6558,13 +6561,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6615,7 +6618,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6624,7 +6627,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6642,10 +6645,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6656,10 +6659,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6685,16 +6688,16 @@
         <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -6722,10 +6725,10 @@
         <v>118</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -6743,7 +6746,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6767,13 +6770,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6784,10 +6787,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6813,16 +6816,16 @@
         <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -6847,13 +6850,13 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -6871,7 +6874,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -6895,13 +6898,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -6912,10 +6915,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6938,17 +6941,17 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -6997,7 +7000,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7027,7 +7030,7 @@
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7038,10 +7041,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7064,13 +7067,13 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7121,7 +7124,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7148,10 +7151,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7162,10 +7165,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7188,16 +7191,16 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7247,7 +7250,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7274,10 +7277,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7288,10 +7291,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7314,16 +7317,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7373,7 +7376,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7400,10 +7403,10 @@
         <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7414,10 +7417,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7440,19 +7443,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7501,7 +7504,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7528,10 +7531,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7542,10 +7545,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7568,13 +7571,13 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7625,7 +7628,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7655,7 +7658,7 @@
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7666,10 +7669,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7698,7 +7701,7 @@
         <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>143</v>
@@ -7751,7 +7754,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7781,7 +7784,7 @@
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7792,14 +7795,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7821,10 +7824,10 @@
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
@@ -7879,7 +7882,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -7920,10 +7923,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7949,13 +7952,13 @@
         <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>210</v>
@@ -7983,10 +7986,10 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>213</v>
@@ -8007,7 +8010,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>94</v>
@@ -8031,16 +8034,16 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>84</v>
@@ -8048,10 +8051,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8074,19 +8077,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8135,7 +8138,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8159,27 +8162,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8205,16 +8208,16 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8242,10 +8245,10 @@
         <v>211</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8263,7 +8266,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8272,7 +8275,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8293,7 +8296,7 @@
         <v>137</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8304,14 +8307,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8333,16 +8336,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8370,10 +8373,10 @@
         <v>211</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8391,7 +8394,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8415,27 +8418,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8461,16 +8464,16 @@
         <v>85</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8519,7 +8522,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8546,10 +8549,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
 </t>
   </si>
   <si>
-    <t>1859: source value from MICROBIOLOGY - MYCOBACTERIUM &gt; MYCOBACTERIUM - MYCOBACTERIUM &gt; ETIOLOGY FIELD -  NAME (63.05-26 &gt; 63.37-.01 &gt; 61.2-.01)</t>
+    <t>1859: source value from MICROBIOLOGY - MYCOBACTERIUM &gt; MYCOBACTERIUM - MYCOBACTERIUM &gt; ETIOLOGY FIELD - NAME (63.05-26 &gt; 63.39-.01 &gt; 61.2-.01)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyMycobacteriologyObservation-mycobact.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
